--- a/outputs/evaluation/architecture/validation/gemini-3-5/CF_M04/run_2/CF_M04_arch_eval.xlsx
+++ b/outputs/evaluation/architecture/validation/gemini-3-5/CF_M04/run_2/CF_M04_arch_eval.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D12"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -440,6 +440,11 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>f1</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
           <t>mean semantic meaning</t>
         </is>
       </c>
@@ -456,7 +461,10 @@
       <c r="C2" t="n">
         <v>0.7027</v>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" t="n">
+        <v>0.5843</v>
+      </c>
+      <c r="E2" t="inlineStr">
         <is>
           <t>-</t>
         </is>
@@ -475,6 +483,9 @@
         <v>0.7586000000000001</v>
       </c>
       <c r="D3" t="n">
+        <v>0.6377</v>
+      </c>
+      <c r="E3" t="n">
         <v>0.9576</v>
       </c>
     </row>
@@ -491,6 +502,9 @@
         <v>0.5</v>
       </c>
       <c r="D4" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E4" t="n">
         <v>0.8694</v>
       </c>
     </row>
@@ -1226,13 +1240,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr">
         <is>
           <t>AU_24</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
           <t>Data</t>
@@ -1256,13 +1268,11 @@
           <t>CF_M04_P08</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr">
         <is>
           <t>CF_M04_AU23</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1283,7 +1293,6 @@
       <c r="D3" t="n">
         <v>0.7635</v>
       </c>
-      <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1304,7 +1313,6 @@
           <t>['AU_03', 'AU_08', 'AU_09']</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr">
         <is>
           <t>AU_42</t>
@@ -1315,7 +1323,6 @@
           <t>backend, artificial intelligence service, gemini</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1334,7 +1341,6 @@
           <t>CF_M04_AU01, CF_M04_AU013, CF_M04_AU14</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr">
         <is>
           <t>CF_M04_AU15</t>
@@ -1390,13 +1396,11 @@
           <t>['AU_34']</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr">
         <is>
           <t>AU_45</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
           <t>REST</t>
@@ -1420,13 +1424,11 @@
           <t>CF_M04_AU29</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr"/>
       <c r="S4" t="inlineStr">
         <is>
           <t>CF_M04_AU06</t>
         </is>
       </c>
-      <c r="T4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1472,13 +1474,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr">
         <is>
           <t>AU_07</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr">
         <is>
           <t>Database</t>
@@ -1497,14 +1497,11 @@
       <c r="P5" t="n">
         <v>55</v>
       </c>
-      <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr"/>
       <c r="S5" t="inlineStr">
         <is>
           <t>CF_M04_AU10</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -1525,7 +1522,6 @@
       <c r="D6" t="n">
         <v>0.8408</v>
       </c>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1546,7 +1542,6 @@
           <t>['AU_03', 'AU_08', 'AU_09', 'AU_10']</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr">
         <is>
           <t>AU_36</t>
@@ -1557,7 +1552,6 @@
           <t>backend, artificial intelligence service, gemini, chatgpt</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1576,7 +1570,6 @@
           <t>CF_M04_AU09, CF_M04_AU013, CF_M04_AU14</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr">
         <is>
           <t>CF_M04_AU16</t>
@@ -1632,13 +1625,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr">
         <is>
           <t>AU_04</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr">
         <is>
           <t>Domain</t>
@@ -1662,13 +1653,11 @@
           <t>CF_M04_P08</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr">
         <is>
           <t>CF_M04_AU22</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1714,13 +1703,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr">
         <is>
           <t>AU_22</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr">
         <is>
           <t>Presentation Layer</t>
@@ -1744,13 +1731,11 @@
           <t>CF_M04_AU01</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr"/>
       <c r="S8" t="inlineStr">
         <is>
           <t>CF_M04_AU02</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1796,13 +1781,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr">
         <is>
           <t>AU_23</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr">
         <is>
           <t>Domain Layer</t>
@@ -1826,13 +1809,11 @@
           <t>CF_M04_P01</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr">
         <is>
           <t>CF_M04_AU07</t>
         </is>
       </c>
-      <c r="T9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1853,7 +1834,6 @@
       <c r="D10" t="n">
         <v>0.929</v>
       </c>
-      <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1874,7 +1854,6 @@
           <t>['AU_03', 'AU_08']</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr">
         <is>
           <t>AU_38</t>
@@ -1885,7 +1864,6 @@
           <t>backend, artificial intelligence service</t>
         </is>
       </c>
-      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1904,7 +1882,6 @@
           <t>CF_M04_AU04, CF_M04_AU18</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr">
         <is>
           <t>CF_M04_AU19</t>
@@ -1935,7 +1912,6 @@
       <c r="D11" t="n">
         <v>0.9443</v>
       </c>
-      <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1956,7 +1932,6 @@
           <t>['AU_02', 'AU_03']</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr">
         <is>
           <t>AU_34</t>
@@ -1967,7 +1942,6 @@
           <t>frontend, backend</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
           <t>Connector</t>
@@ -1986,7 +1960,6 @@
           <t>CF_M04_AU01, CF_M04_AU04</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr">
         <is>
           <t>CF_M04_AU29</t>
@@ -2037,14 +2010,11 @@
           <t>71</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr">
         <is>
           <t>P_06</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr"/>
       <c r="M12" t="inlineStr">
         <is>
           <t>Clean Architecture</t>
@@ -2068,13 +2038,11 @@
           <t>CF_M04_AU01</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr"/>
       <c r="S12" t="inlineStr">
         <is>
           <t>CF_M04_P08</t>
         </is>
       </c>
-      <c r="T12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -2120,13 +2088,11 @@
           <t>['AU_07']</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr">
         <is>
           <t>AU_16</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr">
         <is>
           <t>MySQL</t>
@@ -2150,13 +2116,11 @@
           <t>CF_M04_AU10</t>
         </is>
       </c>
-      <c r="R13" t="inlineStr"/>
       <c r="S13" t="inlineStr">
         <is>
           <t>CF_M04_AU11</t>
         </is>
       </c>
-      <c r="T13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -2202,13 +2166,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr">
         <is>
           <t>AU_11</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr"/>
       <c r="M14" t="inlineStr">
         <is>
           <t>Firebase</t>
@@ -2227,14 +2189,11 @@
       <c r="P14" t="n">
         <v>56</v>
       </c>
-      <c r="Q14" t="inlineStr"/>
-      <c r="R14" t="inlineStr"/>
       <c r="S14" t="inlineStr">
         <is>
           <t>CF_M04_AU27</t>
         </is>
       </c>
-      <c r="T14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -2280,13 +2239,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr">
         <is>
           <t>AU_06</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr"/>
       <c r="M15" t="inlineStr">
         <is>
           <t>Infrastructure Layer</t>
@@ -2310,13 +2267,11 @@
           <t>CF_M04_P01</t>
         </is>
       </c>
-      <c r="R15" t="inlineStr"/>
       <c r="S15" t="inlineStr">
         <is>
           <t>CF_M04_AU09</t>
         </is>
       </c>
-      <c r="T15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -2362,13 +2317,11 @@
           <t>['AU_34']</t>
         </is>
       </c>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr">
         <is>
           <t>AU_31</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr"/>
       <c r="M16" t="inlineStr">
         <is>
           <t>HTTP</t>
@@ -2392,13 +2345,11 @@
           <t>CF_M04_AU06</t>
         </is>
       </c>
-      <c r="R16" t="inlineStr"/>
       <c r="S16" t="inlineStr">
         <is>
           <t>CF_M04_AU17</t>
         </is>
       </c>
-      <c r="T16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -2444,13 +2395,11 @@
           <t>['P_02']</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr">
         <is>
           <t>P_05</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr">
         <is>
           <t>Factory Pattern</t>
@@ -2474,13 +2423,11 @@
           <t>CF_M04_AU04</t>
         </is>
       </c>
-      <c r="R17" t="inlineStr"/>
       <c r="S17" t="inlineStr">
         <is>
           <t>CF_M04_P06</t>
         </is>
       </c>
-      <c r="T17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -2521,14 +2468,11 @@
           <t>55</t>
         </is>
       </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr">
         <is>
           <t>AU_03</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr"/>
       <c r="M18" t="inlineStr">
         <is>
           <t>Backend</t>
@@ -2547,14 +2491,11 @@
       <c r="P18" t="n">
         <v>55</v>
       </c>
-      <c r="Q18" t="inlineStr"/>
-      <c r="R18" t="inlineStr"/>
       <c r="S18" t="inlineStr">
         <is>
           <t>CF_M04_AU04</t>
         </is>
       </c>
-      <c r="T18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -2600,13 +2541,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr">
         <is>
           <t>AU_05</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
           <t>Application Layer</t>
@@ -2630,13 +2569,11 @@
           <t>CF_M04_P01</t>
         </is>
       </c>
-      <c r="R19" t="inlineStr"/>
       <c r="S19" t="inlineStr">
         <is>
           <t>CF_M04_AU08</t>
         </is>
       </c>
-      <c r="T19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2677,14 +2614,11 @@
           <t>54</t>
         </is>
       </c>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr">
         <is>
           <t>AU_02</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
           <t>Frontend</t>
@@ -2703,14 +2637,11 @@
       <c r="P20" t="n">
         <v>54</v>
       </c>
-      <c r="Q20" t="inlineStr"/>
-      <c r="R20" t="inlineStr"/>
       <c r="S20" t="inlineStr">
         <is>
           <t>CF_M04_AU01</t>
         </is>
       </c>
-      <c r="T20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2756,13 +2687,11 @@
           <t>['AU_35']</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr">
         <is>
           <t>AU_46</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr">
         <is>
           <t>ORM</t>
@@ -2786,13 +2715,11 @@
           <t>CF_M04_AU04</t>
         </is>
       </c>
-      <c r="R21" t="inlineStr"/>
       <c r="S21" t="inlineStr">
         <is>
           <t>CF_M04_P07</t>
         </is>
       </c>
-      <c r="T21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2838,13 +2765,11 @@
           <t>['AU_08']</t>
         </is>
       </c>
-      <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr">
         <is>
           <t>AU_09</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr"/>
       <c r="M22" t="inlineStr">
         <is>
           <t>Gemini</t>
@@ -2863,14 +2788,11 @@
       <c r="P22" t="n">
         <v>55</v>
       </c>
-      <c r="Q22" t="inlineStr"/>
-      <c r="R22" t="inlineStr"/>
       <c r="S22" t="inlineStr">
         <is>
           <t>CF_M04_AU14</t>
         </is>
       </c>
-      <c r="T22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2916,13 +2838,11 @@
           <t>['AU_03']</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr">
         <is>
           <t>AU_14</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr"/>
       <c r="M23" t="inlineStr">
         <is>
           <t>Django</t>
@@ -2946,13 +2866,11 @@
           <t>CF_M04_AU04</t>
         </is>
       </c>
-      <c r="R23" t="inlineStr"/>
       <c r="S23" t="inlineStr">
         <is>
           <t>CF_M04_AU05</t>
         </is>
       </c>
-      <c r="T23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2998,13 +2916,11 @@
           <t>['P_02']</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr">
         <is>
           <t>P_04</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
           <t>Repository Pattern</t>
@@ -3028,13 +2944,11 @@
           <t>CF_M04_AU09</t>
         </is>
       </c>
-      <c r="R24" t="inlineStr"/>
       <c r="S24" t="inlineStr">
         <is>
           <t>CF_M04_P05</t>
         </is>
       </c>
-      <c r="T24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -3080,13 +2994,11 @@
           <t>['AU_08']</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr">
         <is>
           <t>AU_10</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr">
         <is>
           <t>ChatGPT</t>
@@ -3105,14 +3017,11 @@
       <c r="P25" t="n">
         <v>55</v>
       </c>
-      <c r="Q25" t="inlineStr"/>
-      <c r="R25" t="inlineStr"/>
       <c r="S25" t="inlineStr">
         <is>
           <t>CF_M04_AU13</t>
         </is>
       </c>
-      <c r="T25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -3153,14 +3062,11 @@
           <t>55</t>
         </is>
       </c>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr">
         <is>
           <t>P_02</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr">
         <is>
           <t>Hexagonal Architecture</t>
@@ -3186,13 +3092,11 @@
           <t>CF_M04_AU04</t>
         </is>
       </c>
-      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr">
         <is>
           <t>CF_M04_P01</t>
         </is>
       </c>
-      <c r="T26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -3238,13 +3142,11 @@
           <t>['AU_02']</t>
         </is>
       </c>
-      <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr">
         <is>
           <t>AU_12</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr"/>
       <c r="M27" t="inlineStr">
         <is>
           <t>Flutter</t>
@@ -3268,13 +3170,11 @@
           <t>CF_M04_AU01, CF_M04_AU03</t>
         </is>
       </c>
-      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr">
         <is>
           <t>CF_M04_AU03</t>
         </is>
       </c>
-      <c r="T27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -3348,7 +3248,6 @@
           <t>Localboss</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
       <c r="E2" t="inlineStr">
         <is>
           <t>Localboss és una empresa petita que es va crear a finals del 2021 amb un objectiu molt clar: desenvolupar una aplicació mòbil que permeti als propietaris de negocis gestionar les seves ressenyes a Google Maps.</t>
@@ -3384,7 +3283,6 @@
           <t>Artificial Intelligence Service</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>Finalment, el sistema integra diversos serveis externs a través del back-end, com ara serveis d’intel·ligència artificial (Gemini o ChatGPT) i serveis d’autenticació.</t>
@@ -3395,7 +3293,6 @@
           <t>CF_M04_AU15</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>0.7388</v>
       </c>
@@ -3416,7 +3313,6 @@
           <t>Dart</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Front-End: Flutter (Dart), utilitzat per al desenvolupament multiplataforma de l’aplicació mòbil per a Android i iOS.</t>
@@ -3452,7 +3348,6 @@
           <t>Python</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
       <c r="E5" t="inlineStr">
         <is>
           <t>Back-End: Django (Python), utilitzat com a framework principal per a la construcció de l’API REST.</t>
@@ -3488,7 +3383,6 @@
           <t>Jira</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Jira per a la gestió de requisits i tasques.</t>
@@ -3524,7 +3418,6 @@
           <t>Git</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr">
         <is>
           <t>Git com a sistema de control de versions.</t>
@@ -3560,7 +3453,6 @@
           <t>Android Studio</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Android Studio i VS Code com a entorns de desenvolupament.</t>
@@ -3596,7 +3488,6 @@
           <t>VS Code</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
       <c r="E9" t="inlineStr">
         <is>
           <t>Android Studio i VS Code com a entorns de desenvolupament.</t>
@@ -3632,7 +3523,6 @@
           <t>Google OAuth 2.0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>Presenta les opcions d'autenticació disponibles, destacant el mètode principal mitjançant Google OAuth 2.0.</t>
@@ -3668,7 +3558,6 @@
           <t>syncfusion_flutter_charts</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>syncfusion_flutter_charts: utilitzada per a la creació de gràfics avançats a la nova pantalla Home, substituint paquets anteriors desactualitzats.</t>
@@ -3704,7 +3593,6 @@
           <t>fl_chart</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>fl_chart: emprada per a la implementació de gràfics lineals, funcionalitat no suportada pels paquets anteriors.</t>
@@ -3740,7 +3628,6 @@
           <t>SliverAppBar</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr"/>
       <c r="E13" t="inlineStr">
         <is>
           <t>SliverAppBar: utilitzada per implementar una App Bar avançada amb comportament dinàmic en funció de l’scroll.</t>
@@ -3776,7 +3663,6 @@
           <t>video_player</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
       <c r="E14" t="inlineStr">
         <is>
           <t>video_player: incorporada per permetre la reproducció de vídeos associats a les reviews.</t>
@@ -3812,7 +3698,6 @@
           <t>Postman</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
       <c r="E15" t="inlineStr">
         <is>
           <t>Postman per provar i validar els endpoints del backend abans de la seva integració al front-end.</t>
@@ -3848,7 +3733,6 @@
           <t>GitHub</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
       <c r="E16" t="inlineStr">
         <is>
           <t>GitHub per a la gestió del codi, pull requests i revisions.</t>
@@ -3884,7 +3768,6 @@
           <t>JSON</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
       <c r="E17" t="inlineStr">
         <is>
           <t>La comunicació entre el front-end i el back-end es realitza mitjançant una API REST, utilitzant missatges en format JSON tant per a les peticions com per a les respostes.</t>
@@ -3895,7 +3778,6 @@
           <t>CF_M04_AU29</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr"/>
       <c r="H17" t="n">
         <v>0.7808</v>
       </c>
@@ -3911,7 +3793,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C18" t="inlineStr"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>frontend, backend</t>
@@ -3947,7 +3828,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>backend, mysql database</t>
@@ -3983,7 +3863,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>frontend, backend</t>
@@ -3999,7 +3878,6 @@
           <t>CF_M04_AU19</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr"/>
       <c r="H20" t="n">
         <v>0.7847</v>
       </c>
@@ -4015,7 +3893,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C21" t="inlineStr"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>frontend, backend</t>
@@ -4031,7 +3908,6 @@
           <t>CF_M04_AU19</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr"/>
       <c r="H21" t="n">
         <v>0.7792</v>
       </c>
@@ -4047,7 +3923,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C22" t="inlineStr"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>backend, artificial intelligence service</t>
@@ -4063,7 +3938,6 @@
           <t>CF_M04_AU19</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr"/>
       <c r="H22" t="n">
         <v>0.759</v>
       </c>
@@ -4079,7 +3953,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C23" t="inlineStr"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>frontend, backend</t>
@@ -4115,7 +3988,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C24" t="inlineStr"/>
       <c r="D24" t="inlineStr">
         <is>
           <t>backend, artificial intelligence service, gemini</t>
@@ -4151,7 +4023,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>frontend, backend</t>
@@ -4192,7 +4063,6 @@
           <t>Client-Server</t>
         </is>
       </c>
-      <c r="D26" t="inlineStr"/>
       <c r="E26" t="inlineStr">
         <is>
           <t>Des del punt de vista de l’usuari, la interacció amb el sistema es realitza a través d’una aplicació mòbil desenvolupada amb Flutter, que actua com a capa de presentació (front-end)... Aquesta aplicació s’encarrega de gestionar la interfície gràfica... així com de realitzar les peticions necessàries al back-end...</t>
@@ -4228,7 +4098,6 @@
           <t>Dependency Inversion Principle</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
       <c r="E27" t="inlineStr">
         <is>
           <t>Inversió de Dependència (DIP): El domini defineix interfícies que són implementades per la infraestructura.</t>
@@ -4315,7 +4184,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr">
         <is>
           <t>application layer, domain layer, infrastructure layer</t>
@@ -4356,7 +4224,6 @@
           <t>Authentication Service</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
       <c r="E3" t="inlineStr">
         <is>
           <t>The back-end, in turn, delegates the code generation to a specialized authentication service, responsible for creating and send the OTP to the user.</t>
@@ -4367,7 +4234,6 @@
           <t>AU_40</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr"/>
       <c r="H3" t="n">
         <v>0.7282999999999999</v>
       </c>
@@ -4388,7 +4254,6 @@
           <t>User</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
       <c r="E4" t="inlineStr">
         <is>
           <t>Users: Application customers who use the new features and provide feedback.</t>
@@ -4419,7 +4284,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>frontend</t>
@@ -4435,7 +4299,6 @@
           <t>AU_37</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr"/>
       <c r="H5" t="n">
         <v>0.7454</v>
       </c>
@@ -4456,7 +4319,6 @@
           <t>Presentation Layer</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
       <c r="E6" t="inlineStr">
         <is>
           <t>Presentation: manages the application state and communication with the interface user via Bloc/Cubit.</t>
@@ -4487,7 +4349,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
           <t>backend, database</t>
@@ -4528,7 +4389,6 @@
           <t>Google Login</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr">
         <is>
           <t>Authentication services, such as Google login.</t>
@@ -4559,7 +4419,6 @@
           <t>Connector</t>
         </is>
       </c>
-      <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>data, backend</t>
@@ -4600,7 +4459,6 @@
           <t>Hierarchical model</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
       <c r="E10" t="inlineStr">
         <is>
           <t>The app's navigation mainly follows a hierarchical model, in which the user accesses the main functionalities from a reduced set of base screens.</t>
@@ -4636,7 +4494,6 @@
           <t>Modular architecture</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
       <c r="E11" t="inlineStr">
         <is>
           <t>Internally, the front-end of the application follows a modular architecture based on features, where code is organized by functionality rather than by type components.</t>
@@ -4672,7 +4529,6 @@
           <t>Bloc/Cubit</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr"/>
       <c r="E12" t="inlineStr">
         <is>
           <t>For state and business logic management, the Bloc pattern is used, specificallythrough its Cubit variant, widely used in Flutter applications modern.</t>
